--- a/Koordinater platser.xlsx
+++ b/Koordinater platser.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/187424d88c890b2a/00 Kjellsson/07_Arrangemang/01_Byathlon/01_Webpage_Byathlon/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6D5DB61A-09F8-49D2-ADE5-5AF676A73321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{6D5DB61A-09F8-49D2-ADE5-5AF676A73321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{85A10AF0-C412-4CCD-9F84-351E4355B692}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{0A28B3E8-859F-4827-8774-5070B154A808}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{0A28B3E8-859F-4827-8774-5070B154A808}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterate="1" iterateCount="5000" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="37">
   <si>
     <t xml:space="preserve">plats namn </t>
   </si>
@@ -68,18 +68,12 @@
     <t>Bastu</t>
   </si>
   <si>
-    <t>63°18'01.8"N 18°19'45.2"E</t>
-  </si>
-  <si>
     <t>Toalett/dass</t>
   </si>
   <si>
     <t>63°18'01.7"N 18°19'44.5"E</t>
   </si>
   <si>
-    <t>63°18'02.0"N 18°19'54.3"E</t>
-  </si>
-  <si>
     <t>63°18'02.3"N 18°19'45.0"E</t>
   </si>
   <si>
@@ -153,6 +147,9 @@
   </si>
   <si>
     <t>63°18'02.7"N 18°19'49.1"E</t>
+  </si>
+  <si>
+    <t>63°18'01.8"N 18°19'45.2"E &amp; 63°18'02.0"N 18°19'54.3"E</t>
   </si>
 </sst>
 </file>
@@ -208,7 +205,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office-tema">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -571,114 +568,111 @@
         <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C14" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" t="s">
         <v>25</v>
       </c>
-      <c r="C16" t="s">
+      <c r="E16" t="s">
         <v>26</v>
-      </c>
-      <c r="D16" t="s">
-        <v>27</v>
-      </c>
-      <c r="E16" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C17" t="s">
+        <v>27</v>
+      </c>
+      <c r="D17" t="s">
+        <v>28</v>
+      </c>
+      <c r="E17" t="s">
         <v>29</v>
       </c>
-      <c r="D17" t="s">
+      <c r="F17" t="s">
         <v>30</v>
-      </c>
-      <c r="E17" t="s">
-        <v>31</v>
-      </c>
-      <c r="F17" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B19" t="s">
+        <v>31</v>
+      </c>
+      <c r="C19" t="s">
+        <v>32</v>
+      </c>
+      <c r="D19" t="s">
         <v>33</v>
       </c>
-      <c r="C19" t="s">
+      <c r="E19" t="s">
         <v>34</v>
       </c>
-      <c r="D19" t="s">
+      <c r="F19" t="s">
         <v>35</v>
-      </c>
-      <c r="E19" t="s">
-        <v>36</v>
-      </c>
-      <c r="F19" t="s">
-        <v>37</v>
       </c>
     </row>
   </sheetData>
